--- a/artfynd/A 9449-2026 artfynd.xlsx
+++ b/artfynd/A 9449-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>430650</v>
+        <v>430649</v>
       </c>
       <c r="B2" t="n">
-        <v>73592</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>528025.5444781622</v>
+        <v>528032</v>
       </c>
       <c r="R2" t="n">
-        <v>6227923.654488129</v>
+        <v>6227917</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>2008-02-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2008-02-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>430649</v>
+        <v>430650</v>
       </c>
       <c r="B3" t="n">
-        <v>73592</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75390</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528031.7198571943</v>
+        <v>528026</v>
       </c>
       <c r="R3" t="n">
-        <v>6227917.019507136</v>
+        <v>6227924</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,19 +854,9 @@
           <t>2008-02-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-02-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>80920495</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528130.950013015</v>
+        <v>528131</v>
       </c>
       <c r="R4" t="n">
-        <v>6228001.112983695</v>
+        <v>6228001</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,19 +969,9 @@
           <t>2019-06-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-06-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +996,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>83601736</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ask (Skyddsvärt träd), Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>528020</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6227857</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Förkärla</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>37399440-D36D-4EAF-9964-D088789D1C00</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-02-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-02-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Karlsson, Annika Lydänge</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
